--- a/backtest_runs/20260410_193731/by_symbol/ECOP/ECOP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ECOP/ECOP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-5054.939999999992</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>94945.06000000001</v>
@@ -633,7 +633,7 @@
         <v>-4340.100000000008</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>90604.95999999999</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>90604.95999999999</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>91090.03000000001</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>91090.03000000001</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>93055.84000000003</v>
@@ -1093,7 +1093,7 @@
         <v>-3421.020000000009</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>89634.82000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-1838.159999999997</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>87796.66000000002</v>
@@ -1231,7 +1231,7 @@
         <v>-408.4800000000095</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>87388.18000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-6203.789999999999</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>81184.39000000001</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>81184.39000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-995.6700000000014</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>83737.39000000001</v>
